--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-same.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-same.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{166ED151-E18A-4F12-B520-458845BB9DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D0561FD-E49A-4976-9272-85F321FB4FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{1976837B-D726-4331-ADCB-806B0EFC8EC7}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{67A29CEB-137C-4CEC-8A1D-15DF0F9614A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576866435185" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{F8318CCA-11D9-43A1-B0F0-182F2252945F}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579428240744" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{2EA7E679-2A22-4D67-A423-13BD5AB9C5C1}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E00EF0A-FB38-4215-BAE7-584CAAF610CF}" name="AllErrorPivot" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94FB296D-907D-445E-B5B5-49BC69107F61}" name="AllErrorPivot" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -537,7 +537,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A5BF253-6789-48A1-84C8-D59DA137613A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DDAA5A5-7D85-4825-9342-60D7C05EBF50}">
   <dimension ref="A4:B8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A1EA868-4D59-4AC2-B756-057B76C18884}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05ABBD8D-68E8-40E2-A846-812DC98BC63B}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
